--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-reversed.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-reversed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4B905C9-C024-4CEA-BC79-78ADDE0CA3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC36110-5CCA-47F9-83CE-19A6A2E40817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{5BAC11E1-16F0-4264-82D2-8DCDA629CB42}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{1CD4B083-719C-4FC0-9C03-E4A2B4A775A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576855439816" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{F4EC3081-3DBD-4617-A062-1253AD473D00}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579418402776" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{A078DBF6-F85A-4AF8-BFFB-45284BF28DBB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46BC1C80-6533-4E3E-9AC3-1870CC31845D}" name="AllErrorPivot" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1340A875-02DD-4F5D-9ABA-F3BD21B8630A}" name="AllErrorPivot" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D2B16-6D89-4D3E-8E87-403FB06B5C5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767735BC-A164-442A-9F53-382F01BC73E1}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B221A8A-1C03-45A2-9771-CB5FA0B618D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3EB9EB-A508-4EE6-9285-F51A2FB44A9B}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
